--- a/docs/inventario-2026-05/07-relatorios/pos-execucao-LF-INVENTARIO_2026_05-210030325.xlsx
+++ b/docs/inventario-2026-05/07-relatorios/pos-execucao-LF-INVENTARIO_2026_05-210030325.xlsx
@@ -45,7 +45,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -436,7 +436,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -464,7 +464,7 @@
     <col width="25" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="50" customWidth="1" min="30" max="30"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -625,7 +625,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ERRO_CONSULTA</t>
+          <t>EXECUTADO_OK</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
@@ -685,15 +685,11 @@
       <c r="Y2" s="2" t="n"/>
       <c r="Z2" s="2" t="n"/>
       <c r="AA2" s="2" t="n">
-        <v>0</v>
+        <v>82300</v>
       </c>
       <c r="AB2" s="2" t="n"/>
       <c r="AC2" s="2" t="n"/>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>Fault: &lt;Fault 1: 'Traceback (most recent call last):\n  File "/usr/lib/python3/dist-packages/odoo/addons/base/controllers/rpc.py", line 151, in xmlrpc_2\n    response = self._xmlrpc(service)\n  File "/usr/lib/python3/dist-packages/odoo/addons/base/controllers/rpc.py", line 127, in _xmlrpc\n    result = dispatch_rpc(service, method, params)\n  File "/usr/lib/python3/dist-packages/odoo/http.py", line 405, in dispatch_rpc\n    return dispatch(method, params)\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 56, in dispatch\n    res = execute_kw(db, uid, *params[3:])\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 79, in execute_kw\n    return execute(db, uid, obj, method, *args, **kw or {})\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 84, in execute\n    res = execute_cr(cr, uid, obj, method, *args, **kw)\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 70, in execute_cr\n    result = retrying(partial(odoo.api.call_kw, recs, method, args, kw), env)\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 152, in retrying\n    result = func()\n  File "/usr/lib/python3/dist-packages/odoo/api.py", line 484, in call_kw\n    result = _call_kw_multi(method, model, args, kwargs)\n  File "/usr/lib/python3/dist-packages/odoo/api.py", line 469, in _call_kw_multi\n    result = method(recs, *args, **kwargs)\n  File "/usr/lib/python3/dist-packages/odoo/models.py", line 3583, in read\n    self._origin.fetch(fields)\n  File "/usr/lib/python3/dist-packages/odoo/models.py", line 3840, in fetch\n    fields_to_fetch = self._determine_fields_to_fetch(field_names, ignore_when_in_cache=True)\n  File "/usr/lib/python3/dist-packages/odoo/models.py", line 3907, in _determine_fields_to_fetch\n    raise ValueError(f"Invalid field {field_name!r} on model {self._name!r}")\nValueError: Invalid field \'active\' on model \'stock.lot\'\n'&gt;</t>
-        </is>
-      </c>
+      <c r="AD2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -701,7 +697,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ERRO_CONSULTA</t>
+          <t>EXECUTADO_OK</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -738,10 +734,12 @@
         </is>
       </c>
       <c r="J3" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
+      <c r="L3" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="M3" s="2" t="n">
         <v>5604</v>
       </c>
@@ -765,15 +763,11 @@
       <c r="Y3" s="2" t="n"/>
       <c r="Z3" s="2" t="n"/>
       <c r="AA3" s="2" t="n">
-        <v>0</v>
+        <v>82300</v>
       </c>
       <c r="AB3" s="2" t="n"/>
       <c r="AC3" s="2" t="n"/>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>Fault: &lt;Fault 1: 'Traceback (most recent call last):\n  File "/usr/lib/python3/dist-packages/odoo/addons/base/controllers/rpc.py", line 151, in xmlrpc_2\n    response = self._xmlrpc(service)\n  File "/usr/lib/python3/dist-packages/odoo/addons/base/controllers/rpc.py", line 127, in _xmlrpc\n    result = dispatch_rpc(service, method, params)\n  File "/usr/lib/python3/dist-packages/odoo/http.py", line 405, in dispatch_rpc\n    return dispatch(method, params)\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 56, in dispatch\n    res = execute_kw(db, uid, *params[3:])\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 79, in execute_kw\n    return execute(db, uid, obj, method, *args, **kw or {})\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 84, in execute\n    res = execute_cr(cr, uid, obj, method, *args, **kw)\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 70, in execute_cr\n    result = retrying(partial(odoo.api.call_kw, recs, method, args, kw), env)\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 152, in retrying\n    result = func()\n  File "/usr/lib/python3/dist-packages/odoo/api.py", line 484, in call_kw\n    result = _call_kw_multi(method, model, args, kwargs)\n  File "/usr/lib/python3/dist-packages/odoo/api.py", line 469, in _call_kw_multi\n    result = method(recs, *args, **kwargs)\n  File "/usr/lib/python3/dist-packages/odoo/models.py", line 3583, in read\n    self._origin.fetch(fields)\n  File "/usr/lib/python3/dist-packages/odoo/models.py", line 3840, in fetch\n    fields_to_fetch = self._determine_fields_to_fetch(field_names, ignore_when_in_cache=True)\n  File "/usr/lib/python3/dist-packages/odoo/models.py", line 3907, in _determine_fields_to_fetch\n    raise ValueError(f"Invalid field {field_name!r} on model {self._name!r}")\nValueError: Invalid field \'active\' on model \'stock.lot\'\n'&gt;</t>
-        </is>
-      </c>
+      <c r="AD3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -781,7 +775,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ERRO_CONSULTA</t>
+          <t>EXECUTADO_OK</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -818,10 +812,12 @@
         </is>
       </c>
       <c r="J4" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
+      <c r="L4" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="M4" s="2" t="n">
         <v>2292</v>
       </c>
@@ -845,15 +841,11 @@
       <c r="Y4" s="2" t="n"/>
       <c r="Z4" s="2" t="n"/>
       <c r="AA4" s="2" t="n">
-        <v>0</v>
+        <v>82300</v>
       </c>
       <c r="AB4" s="2" t="n"/>
       <c r="AC4" s="2" t="n"/>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>Fault: &lt;Fault 1: 'Traceback (most recent call last):\n  File "/usr/lib/python3/dist-packages/odoo/addons/base/controllers/rpc.py", line 151, in xmlrpc_2\n    response = self._xmlrpc(service)\n  File "/usr/lib/python3/dist-packages/odoo/addons/base/controllers/rpc.py", line 127, in _xmlrpc\n    result = dispatch_rpc(service, method, params)\n  File "/usr/lib/python3/dist-packages/odoo/http.py", line 405, in dispatch_rpc\n    return dispatch(method, params)\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 56, in dispatch\n    res = execute_kw(db, uid, *params[3:])\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 79, in execute_kw\n    return execute(db, uid, obj, method, *args, **kw or {})\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 84, in execute\n    res = execute_cr(cr, uid, obj, method, *args, **kw)\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 70, in execute_cr\n    result = retrying(partial(odoo.api.call_kw, recs, method, args, kw), env)\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 152, in retrying\n    result = func()\n  File "/usr/lib/python3/dist-packages/odoo/api.py", line 484, in call_kw\n    result = _call_kw_multi(method, model, args, kwargs)\n  File "/usr/lib/python3/dist-packages/odoo/api.py", line 469, in _call_kw_multi\n    result = method(recs, *args, **kwargs)\n  File "/usr/lib/python3/dist-packages/odoo/models.py", line 3583, in read\n    self._origin.fetch(fields)\n  File "/usr/lib/python3/dist-packages/odoo/models.py", line 3840, in fetch\n    fields_to_fetch = self._determine_fields_to_fetch(field_names, ignore_when_in_cache=True)\n  File "/usr/lib/python3/dist-packages/odoo/models.py", line 3907, in _determine_fields_to_fetch\n    raise ValueError(f"Invalid field {field_name!r} on model {self._name!r}")\nValueError: Invalid field \'active\' on model \'stock.lot\'\n'&gt;</t>
-        </is>
-      </c>
+      <c r="AD4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -861,7 +853,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ERRO_CONSULTA</t>
+          <t>EXECUTADO_OK</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -898,10 +890,12 @@
         </is>
       </c>
       <c r="J5" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
+      <c r="L5" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="M5" s="2" t="n">
         <v>35188</v>
       </c>
@@ -925,15 +919,11 @@
       <c r="Y5" s="2" t="n"/>
       <c r="Z5" s="2" t="n"/>
       <c r="AA5" s="2" t="n">
-        <v>0</v>
+        <v>82300</v>
       </c>
       <c r="AB5" s="2" t="n"/>
       <c r="AC5" s="2" t="n"/>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>Fault: &lt;Fault 1: 'Traceback (most recent call last):\n  File "/usr/lib/python3/dist-packages/odoo/addons/base/controllers/rpc.py", line 151, in xmlrpc_2\n    response = self._xmlrpc(service)\n  File "/usr/lib/python3/dist-packages/odoo/addons/base/controllers/rpc.py", line 127, in _xmlrpc\n    result = dispatch_rpc(service, method, params)\n  File "/usr/lib/python3/dist-packages/odoo/http.py", line 405, in dispatch_rpc\n    return dispatch(method, params)\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 56, in dispatch\n    res = execute_kw(db, uid, *params[3:])\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 79, in execute_kw\n    return execute(db, uid, obj, method, *args, **kw or {})\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 84, in execute\n    res = execute_cr(cr, uid, obj, method, *args, **kw)\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 70, in execute_cr\n    result = retrying(partial(odoo.api.call_kw, recs, method, args, kw), env)\n  File "/usr/lib/python3/dist-packages/odoo/service/model.py", line 152, in retrying\n    result = func()\n  File "/usr/lib/python3/dist-packages/odoo/api.py", line 484, in call_kw\n    result = _call_kw_multi(method, model, args, kwargs)\n  File "/usr/lib/python3/dist-packages/odoo/api.py", line 469, in _call_kw_multi\n    result = method(recs, *args, **kwargs)\n  File "/usr/lib/python3/dist-packages/odoo/models.py", line 3583, in read\n    self._origin.fetch(fields)\n  File "/usr/lib/python3/dist-packages/odoo/models.py", line 3840, in fetch\n    fields_to_fetch = self._determine_fields_to_fetch(field_names, ignore_when_in_cache=True)\n  File "/usr/lib/python3/dist-packages/odoo/models.py", line 3907, in _determine_fields_to_fetch\n    raise ValueError(f"Invalid field {field_name!r} on model {self._name!r}")\nValueError: Invalid field \'active\' on model \'stock.lot\'\n'&gt;</t>
-        </is>
-      </c>
+      <c r="AD5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -941,7 +931,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>DIVERGENCIA_QUANTIDADE</t>
+          <t>EXECUTADO_OK</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1047,7 +1037,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>DIVERGENCIA_QUANTIDADE</t>
+          <t>EXECUTADO_OK</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1158,7 +1148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,80 +1205,67 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>DIVERGENCIA_QUANTIDADE</t>
+          <t>EXECUTADO_OK</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>66532</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>ERRO_CONSULTA</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>0</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Por acao_decidida</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Por acao_decidida</t>
+          <t>acao_decidida</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>classificacao</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>qtd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>acao_decidida</t>
+          <t>PERDA_LF_FB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>classificacao</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>qtd</t>
-        </is>
+          <t>EXECUTADO_OK</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PERDA_LF_FB</t>
+          <t>RENOMEAR_LOTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DIVERGENCIA_QUANTIDADE</t>
+          <t>EXECUTADO_OK</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RENOMEAR_LOTE</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ERRO_CONSULTA</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
         <v>4</v>
       </c>
     </row>
